--- a/owlcms/src/main/resources/templates/cards/ZAccreditation.xlsx
+++ b/owlcms/src/main/resources/templates/cards/ZAccreditation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lamyj\git\owlcms4\owlcms\src\main\resources\templates\cards\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7B44381-1FAE-404A-A990-26C9DFAEBCCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{033A5B13-929F-4F08-9093-169130D6129C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26955" yWindow="8010" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="5295" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -52,6 +52,16 @@
           <t xml:space="preserve">
 </t>
         </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>jx:each(items="athletes" var="a" lastCell="A2")</t>
+        </r>
       </text>
     </comment>
     <comment ref="A2" authorId="0" shapeId="0" xr:uid="{C02540E0-E6B2-44DA-9011-74B85107445B}">
@@ -64,7 +74,7 @@
             <rFont val="Tahoma"/>
             <charset val="1"/>
           </rPr>
-          <t>jx:image(src="local.getBytes('_pictures/4123.jpg')" imageType="JPEG"  lastCell="A2")</t>
+          <t>jx:image(src="local.getBytes('_pictures/'+a.membership+'.jpg')" imageType="JPEG" lastCell="A2")</t>
         </r>
         <r>
           <rPr>
@@ -85,14 +95,14 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
   <si>
-    <t>${t.get('Group')}</t>
+    <t>${a.fullName}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -112,6 +122,21 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -134,8 +159,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -419,17 +447,18 @@
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="42.28515625" customWidth="1"/>
+    <col min="1" max="1" width="65.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="207" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:1" ht="409.5" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="70" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/owlcms/src/main/resources/templates/cards/ZAccreditation.xlsx
+++ b/owlcms/src/main/resources/templates/cards/ZAccreditation.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lamyj\git\owlcms4\owlcms\src\main\resources\templates\cards\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\git\owlcms_v23\owlcms\src\main\resources\templates\cards\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{033A5B13-929F-4F08-9093-169130D6129C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{109AC222-4DCA-4196-8736-481915E15955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="5295" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -74,7 +74,7 @@
             <rFont val="Tahoma"/>
             <charset val="1"/>
           </rPr>
-          <t>jx:image(src="local.getBytes('_pictures/'+a.membership+'.jpg')" imageType="JPEG" lastCell="A2")</t>
+          <t>jx:image(src="local.getBytes('pictures/'+a.membership+'.jpg')" imageType="JPEG" lastCell="A2")</t>
         </r>
         <r>
           <rPr>

--- a/owlcms/src/main/resources/templates/cards/ZAccreditation.xlsx
+++ b/owlcms/src/main/resources/templates/cards/ZAccreditation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\git\owlcms_v23\owlcms\src\main\resources\templates\cards\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\git\owlcms_v23stable\owlcms_v23master\owlcms\src\main\resources\templates\cards\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{109AC222-4DCA-4196-8736-481915E15955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9579A4B4-E834-4CDB-8795-F81544A5056B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="5295" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
     <author>Jean-François Lamy</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{AA3A3EF9-57C4-4AC3-8B0E-3277D2F61F33}">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{0AFEDE08-05A8-43E9-A9A7-555DE8FC2379}">
       <text>
         <r>
           <rPr>
@@ -40,7 +40,7 @@
             <rFont val="Tahoma"/>
             <charset val="1"/>
           </rPr>
-          <t>jx:area(lastCell="A2")</t>
+          <t>Jean-François Lamy:</t>
         </r>
         <r>
           <rPr>
@@ -50,21 +50,12 @@
             <charset val="1"/>
           </rPr>
           <t xml:space="preserve">
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>jx:each(items="athletes" var="a" lastCell="A2")</t>
+jx:area(lastCell="C6")
+jx:each(items="athletes" var="a" lastCell="C6")</t>
         </r>
       </text>
     </comment>
-    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{C02540E0-E6B2-44DA-9011-74B85107445B}">
+    <comment ref="B4" authorId="0" shapeId="0" xr:uid="{C02540E0-E6B2-44DA-9011-74B85107445B}">
       <text>
         <r>
           <rPr>
@@ -74,7 +65,7 @@
             <rFont val="Tahoma"/>
             <charset val="1"/>
           </rPr>
-          <t>jx:image(src="local.getBytes('pictures/'+a.membership+'.jpg')" imageType="JPEG" lastCell="A2")</t>
+          <t>jx:image(src="local.getBytes('pictures/'+a.membership+'.jpg')" imageType="JPEG" lastCell="B4")</t>
         </r>
         <r>
           <rPr>
@@ -93,16 +84,22 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>${a.fullName}</t>
+  </si>
+  <si>
+    <t>${a.team}</t>
+  </si>
+  <si>
+    <t>${a.group}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -125,13 +122,6 @@
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -147,7 +137,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -155,13 +145,107 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -444,18 +528,50 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="65.5703125" customWidth="1"/>
+    <col min="1" max="1" width="2.42578125" customWidth="1"/>
+    <col min="2" max="2" width="65.5703125" customWidth="1"/>
+    <col min="3" max="3" width="2.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="3"/>
+    </row>
+    <row r="2" spans="1:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4"/>
+      <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
+      <c r="C2" s="6"/>
     </row>
-    <row r="2" spans="1:1" ht="409.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="4"/>
+      <c r="B3" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6"/>
+    </row>
+    <row r="4" spans="1:3" ht="299.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="6"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="4"/>
+      <c r="B5" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="6"/>
+    </row>
+    <row r="6" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="8"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="10"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="70" orientation="portrait" r:id="rId1"/>

--- a/owlcms/src/main/resources/templates/cards/ZAccreditation.xlsx
+++ b/owlcms/src/main/resources/templates/cards/ZAccreditation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\git\owlcms_v23\owlcms\src\main\resources\templates\cards\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ED95A33-AAF0-4310-996D-A0DCDC5BB3DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0211576A-FF11-4CFB-9410-46254E569BAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="5295" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -154,7 +154,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -240,6 +240,14 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="0" tint="-4.9989318521683403E-2"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -523,6 +531,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -559,15 +575,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
@@ -942,13 +950,13 @@
     </row>
     <row r="3" spans="1:9" s="8" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="9"/>
-      <c r="C3" s="42" t="s">
+      <c r="C3" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
       <c r="H3" s="10"/>
     </row>
     <row r="4" spans="1:9" ht="9" customHeight="1" x14ac:dyDescent="0.25">
@@ -962,13 +970,13 @@
     </row>
     <row r="5" spans="1:9" s="14" customFormat="1" ht="66.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B5" s="15"/>
-      <c r="C5" s="29" t="s">
+      <c r="C5" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
       <c r="H5" s="16"/>
     </row>
     <row r="6" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -993,11 +1001,11 @@
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="11"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
       <c r="H8" s="13"/>
     </row>
     <row r="9" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1008,9 +1016,9 @@
     </row>
     <row r="10" spans="1:9" ht="102.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="11"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="32"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="36"/>
       <c r="H10" s="13"/>
     </row>
     <row r="11" spans="1:9" ht="101.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1018,9 +1026,9 @@
       <c r="C11" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="33"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="35"/>
+      <c r="E11" s="37"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="39"/>
       <c r="H11" s="13"/>
     </row>
     <row r="12" spans="1:9" ht="102.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1028,9 +1036,9 @@
       <c r="C12" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="E12" s="36"/>
-      <c r="F12" s="37"/>
-      <c r="G12" s="38"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="42"/>
       <c r="H12" s="13"/>
     </row>
     <row r="13" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1041,33 +1049,33 @@
     </row>
     <row r="14" spans="1:9" s="21" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="22"/>
-      <c r="C14" s="27" t="s">
+      <c r="C14" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="27"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="31"/>
       <c r="H14" s="23"/>
     </row>
     <row r="15" spans="1:9" s="21" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="22"/>
-      <c r="C15" s="27" t="s">
+      <c r="C15" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="27"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="31"/>
       <c r="H15" s="23"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B16" s="11"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="28"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
       <c r="H16" s="13"/>
     </row>
     <row r="17" spans="1:16382" ht="131.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1094,21 +1102,21 @@
     </row>
     <row r="19" spans="1:16382" x14ac:dyDescent="0.25">
       <c r="B19" s="11"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
       <c r="H19" s="13"/>
     </row>
     <row r="20" spans="1:16382" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="39"/>
-      <c r="C20" s="40"/>
-      <c r="D20" s="40"/>
-      <c r="E20" s="40"/>
-      <c r="F20" s="40"/>
-      <c r="G20" s="40"/>
-      <c r="H20" s="41"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="28"/>
     </row>
     <row r="21" spans="1:16382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="17"/>

--- a/owlcms/src/main/resources/templates/cards/ZAccreditation.xlsx
+++ b/owlcms/src/main/resources/templates/cards/ZAccreditation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\git\owlcms_v23\owlcms\src\main\resources\templates\cards\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0211576A-FF11-4CFB-9410-46254E569BAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DE1446D-7CE9-46B9-93E6-FBC0FE3B14B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="5295" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,12 +53,12 @@
             <family val="2"/>
           </rPr>
           <t>jx:area(
-  lastCell="I24"
+  lastCell="I21"
 )
 jx:each(
   items="athletes"
   var="athlete"
-  lastCell="I24"
+  lastCell="I21"
 )</t>
         </r>
       </text>
@@ -73,7 +73,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>jx:image(src="local.getBytes('pictures/'+athlete.membership+'.jpg')" imageType="JPEG" lastCell="G12")</t>
+          <t>jx:image(src="local.getBytes('pictures/'+athlete.membership+'.jpg')" imageType="JPEG" ptHeight="305.25" lastCell="G12")</t>
         </r>
         <r>
           <rPr>
@@ -91,23 +91,12 @@
       <text>
         <r>
           <rPr>
-            <b/>
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Jean-François Lamy:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-jx:image(src="local.getBytes(athlete.teamFlagPath)" imageType="PNG" lastCell="C11")
+          <t xml:space="preserve">jx:image(src="local.getBytes(athlete.teamFlagPath)" imageType="PNG" lastCell="C11")
 </t>
         </r>
       </text>
@@ -475,7 +464,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -548,6 +537,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -575,8 +567,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -990,13 +982,13 @@
     </row>
     <row r="7" spans="1:9" s="14" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B7" s="15"/>
-      <c r="C7" s="43" t="s">
+      <c r="C7" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="43"/>
-      <c r="E7" s="43"/>
-      <c r="F7" s="43"/>
-      <c r="G7" s="43"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
       <c r="H7" s="16"/>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1015,30 +1007,30 @@
       <c r="H9" s="13"/>
     </row>
     <row r="10" spans="1:9" ht="102.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="11"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="36"/>
+      <c r="B10" s="44"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="37"/>
       <c r="H10" s="13"/>
     </row>
     <row r="11" spans="1:9" ht="101.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="11"/>
+      <c r="B11" s="44"/>
       <c r="C11" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="37"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="39"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="40"/>
       <c r="H11" s="13"/>
     </row>
     <row r="12" spans="1:9" ht="102.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="11"/>
+      <c r="B12" s="44"/>
       <c r="C12" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="E12" s="40"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="42"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="43"/>
       <c r="H12" s="13"/>
     </row>
     <row r="13" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -17511,7 +17503,8 @@
       <c r="G23" s="17"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
+    <mergeCell ref="B10:B12"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="C20:G20"/>
     <mergeCell ref="C14:G14"/>

--- a/owlcms/src/main/resources/templates/cards/ZAccreditation.xlsx
+++ b/owlcms/src/main/resources/templates/cards/ZAccreditation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\git\owlcms_v23\owlcms\src\main\resources\templates\cards\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E7341F7-642B-4FF6-9B46-4557E92C03E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C15E4F4B-F2AC-4B09-93A9-8607E389F896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="5295" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -70,7 +70,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>jx:image(src="local.getBytes('pictures/'+athlete.membership+'.jpg')" imageType="JPEG" ptHeight="305.25" lastCell="G12")</t>
+          <t>jx:image(src="local.getBytes('pictures/'+athlete.membership+'.jpg')" imageType="JPEG" ptHeight="295" lastCell="G12")</t>
         </r>
         <r>
           <rPr>
@@ -529,6 +529,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -555,9 +558,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -968,13 +968,13 @@
     </row>
     <row r="7" spans="1:9" s="14" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B7" s="15"/>
-      <c r="C7" s="44" t="s">
+      <c r="C7" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="35"/>
       <c r="H7" s="16"/>
     </row>
     <row r="8" spans="1:9" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -994,9 +994,9 @@
     </row>
     <row r="10" spans="1:9" ht="102.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="29"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="36"/>
-      <c r="G10" s="37"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="38"/>
       <c r="H10" s="13"/>
     </row>
     <row r="11" spans="1:9" ht="101.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1004,9 +1004,9 @@
       <c r="C11" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="E11" s="38"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="40"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="41"/>
       <c r="H11" s="13"/>
     </row>
     <row r="12" spans="1:9" ht="102.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1014,9 +1014,9 @@
       <c r="C12" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="E12" s="41"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="43"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="44"/>
       <c r="H12" s="13"/>
     </row>
     <row r="13" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">

--- a/owlcms/src/main/resources/templates/cards/ZAccreditation.xlsx
+++ b/owlcms/src/main/resources/templates/cards/ZAccreditation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\git\owlcms_v23\owlcms\src\main\resources\templates\cards\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C15E4F4B-F2AC-4B09-93A9-8607E389F896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5853BDE2-40A7-4676-A5FE-C6C2FB41E80B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="5295" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -127,10 +127,10 @@
     <t>Live Feed QR Code</t>
   </si>
   <si>
-    <t>${athlete.group}</t>
+    <t>sponsor logos</t>
   </si>
   <si>
-    <t>sponsor logos</t>
+    <t>${t.get("Group")} ${athlete.group} - ${athlete.group.localizedStartDay} ${athlete.group.localizedStartHour}</t>
   </si>
 </sst>
 </file>
@@ -896,7 +896,7 @@
   <dimension ref="A1:I20"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" customWidth="1"/>
+    <col min="1" max="1" width="0.85546875" customWidth="1"/>
     <col min="2" max="2" width="2.42578125" customWidth="1"/>
     <col min="3" max="3" width="27.7109375" customWidth="1"/>
     <col min="4" max="4" width="3.5703125" customWidth="1"/>
@@ -949,7 +949,7 @@
     <row r="5" spans="1:9" s="14" customFormat="1" ht="66.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B5" s="15"/>
       <c r="C5" s="34" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D5" s="34"/>
       <c r="E5" s="34"/>
@@ -1028,7 +1028,7 @@
     <row r="14" spans="1:9" s="21" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="22"/>
       <c r="C14" s="32" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D14" s="32"/>
       <c r="E14" s="32"/>
@@ -1111,8 +1111,8 @@
     <mergeCell ref="E10:G12"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.01" bottom="0" header="0" footer="0"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0" right="0.39370078740157483" top="0" bottom="0" header="0" footer="0"/>
+  <pageSetup paperSize="9" fitToWidth="0" orientation="portrait" r:id="rId1"/>
   <headerFooter scaleWithDoc="0"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>

--- a/owlcms/src/main/resources/templates/cards/ZAccreditation.xlsx
+++ b/owlcms/src/main/resources/templates/cards/ZAccreditation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\git\owlcms_v23\owlcms\src\main\resources\templates\cards\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5853BDE2-40A7-4676-A5FE-C6C2FB41E80B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E76F6972-B101-46F9-B4B1-58CD96BED0E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,18 +49,12 @@
             <rFont val="Aptos Narrow"/>
             <family val="2"/>
           </rPr>
-          <t>jx:area(
-  lastCell="I20"
-)
-jx:each(
-  items="athletes"
-  var="athlete"
-  lastCell="I20"
-)</t>
+          <t>jx:area(lastCell="I20")
+jx:each( items="athletes"  var="athlete"  lastCell="I20")</t>
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="1" shapeId="0" xr:uid="{BEE1A7AE-B3A3-4E86-9FB4-D5B7C108D7BB}">
+    <comment ref="C3" authorId="1" shapeId="0" xr:uid="{C043C6FA-479E-42C8-8C1E-36427011D03C}">
       <text>
         <r>
           <rPr>
@@ -70,7 +64,8 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>jx:image(src="local.getBytes('pictures/'+athlete.membership+'.jpg')" imageType="JPEG" ptHeight="295" lastCell="G12")</t>
+          <t xml:space="preserve">you can use lines 3 to 5 for competition name and logos -- resize vertically the other lines so the card fits on one page
+</t>
         </r>
         <r>
           <rPr>
@@ -80,6 +75,20 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E10" authorId="1" shapeId="0" xr:uid="{BEE1A7AE-B3A3-4E86-9FB4-D5B7C108D7BB}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">jx:image(src="local.getBytes('pictures/'+athlete.membership+'.jpg')" imageType="JPEG" ptHeight="300" lastCell="G12")
 </t>
         </r>
       </text>
@@ -98,12 +107,77 @@
         </r>
       </text>
     </comment>
+    <comment ref="C17" authorId="1" shapeId="0" xr:uid="{6581A994-AFB7-4F1D-A422-24EF7E4A47EC}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">jx:image(src="local.getBytes('logos/federation.png')" imageType="PNG" ptHeight="120" lastCell="C17")
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E17" authorId="1" shapeId="0" xr:uid="{EBDC0011-9E17-45BC-B768-FC0D2E20431A}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>jx:image(src="local.getBytes('logos/resultsQR.png')" imageType="PNG" ptHeight="120" lastCell="E17")</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G17" authorId="1" shapeId="0" xr:uid="{F51235AC-A6BA-415D-9661-3053A5276DF7}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">jx:image(src="local.getBytes('logos/liveQR.png')" imageType="PNG" ptHeight="120" lastCell="G17")
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C19" authorId="1" shapeId="0" xr:uid="{60660D87-EEFD-4846-AB22-5A697C3896EB}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>jx:image(src="local.getBytes('logos/liveQR.png')" imageType="PNG" ptHeight="100" lastCell="G19")</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>${athlete.fixedName}</t>
   </si>
@@ -118,9 +192,6 @@
 ${athlete.team}</t>
   </si>
   <si>
-    <t>${a.custom1}</t>
-  </si>
-  <si>
     <t>Results QR Code</t>
   </si>
   <si>
@@ -132,6 +203,12 @@
   <si>
     <t>${t.get("Group")} ${athlete.group} - ${athlete.group.localizedStartDay} ${athlete.group.localizedStartHour}</t>
   </si>
+  <si>
+    <t>Federation Logo</t>
+  </si>
+  <si>
+    <t>${a.custom1} ${a.custom2}</t>
+  </si>
 </sst>
 </file>
 
@@ -140,7 +217,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -227,6 +304,14 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="26"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -242,7 +327,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -401,19 +486,6 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -449,11 +521,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -503,21 +612,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -529,34 +635,63 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -897,14 +1032,14 @@
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="0.85546875" customWidth="1"/>
-    <col min="2" max="2" width="2.42578125" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" customWidth="1"/>
-    <col min="4" max="4" width="3.5703125" customWidth="1"/>
-    <col min="5" max="5" width="27.7109375" customWidth="1"/>
-    <col min="6" max="6" width="3.5703125" customWidth="1"/>
-    <col min="7" max="7" width="26.140625" customWidth="1"/>
+    <col min="2" max="2" width="2.7109375" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="4" customWidth="1"/>
+    <col min="5" max="5" width="28" customWidth="1"/>
+    <col min="6" max="6" width="4" customWidth="1"/>
+    <col min="7" max="7" width="28" customWidth="1"/>
     <col min="8" max="8" width="2.7109375" customWidth="1"/>
-    <col min="9" max="9" width="1.7109375" customWidth="1"/>
+    <col min="9" max="9" width="0.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -917,7 +1052,7 @@
       <c r="H1" s="4"/>
       <c r="I1" s="2"/>
     </row>
-    <row r="2" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="5"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
@@ -926,18 +1061,18 @@
       <c r="G2" s="6"/>
       <c r="H2" s="7"/>
     </row>
-    <row r="3" spans="1:9" s="8" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" s="8" customFormat="1" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="9"/>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
       <c r="H3" s="10"/>
     </row>
-    <row r="4" spans="1:9" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="11"/>
       <c r="C4" s="12"/>
       <c r="D4" s="12"/>
@@ -946,15 +1081,13 @@
       <c r="G4" s="12"/>
       <c r="H4" s="13"/>
     </row>
-    <row r="5" spans="1:9" s="14" customFormat="1" ht="66.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:9" s="14" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B5" s="15"/>
-      <c r="C5" s="34" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
       <c r="H5" s="16"/>
     </row>
     <row r="6" spans="1:9" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -966,24 +1099,24 @@
       <c r="G6" s="12"/>
       <c r="H6" s="13"/>
     </row>
-    <row r="7" spans="1:9" s="14" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B7" s="15"/>
-      <c r="C7" s="35" t="s">
+    <row r="7" spans="1:9" s="49" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="50"/>
+      <c r="C7" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="16"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="51"/>
     </row>
     <row r="8" spans="1:9" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="11"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
       <c r="H8" s="13"/>
     </row>
     <row r="9" spans="1:9" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -993,117 +1126,118 @@
       <c r="H9" s="13"/>
     </row>
     <row r="10" spans="1:9" ht="102.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="29"/>
-      <c r="E10" s="36"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="38"/>
+      <c r="B10" s="28"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="36"/>
       <c r="H10" s="13"/>
     </row>
     <row r="11" spans="1:9" ht="101.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="29"/>
+      <c r="B11" s="28"/>
       <c r="C11" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="E11" s="39"/>
-      <c r="F11" s="40"/>
-      <c r="G11" s="41"/>
+      <c r="E11" s="37"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="39"/>
       <c r="H11" s="13"/>
     </row>
     <row r="12" spans="1:9" ht="102.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="29"/>
+      <c r="B12" s="28"/>
       <c r="C12" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="E12" s="42"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="44"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="42"/>
       <c r="H12" s="13"/>
     </row>
-    <row r="13" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="11"/>
       <c r="E13" s="20"/>
       <c r="G13" s="20"/>
       <c r="H13" s="13"/>
     </row>
-    <row r="14" spans="1:9" s="21" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" s="21" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="22"/>
-      <c r="C14" s="32" t="s">
+      <c r="C14" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="23"/>
+    </row>
+    <row r="15" spans="1:9" s="21" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="22"/>
+      <c r="C15" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="23"/>
+    </row>
+    <row r="16" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="11"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="F16" s="45"/>
+      <c r="G16" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="H16" s="13"/>
+    </row>
+    <row r="17" spans="2:8" ht="123" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="11"/>
+      <c r="C17" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="23"/>
-    </row>
-    <row r="15" spans="1:9" s="21" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="22"/>
-      <c r="C15" s="32" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="23"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B16" s="11"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="13"/>
-    </row>
-    <row r="17" spans="2:8" ht="131.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="11"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="24"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="47"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="47"/>
       <c r="H17" s="13"/>
     </row>
-    <row r="18" spans="2:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="11"/>
-      <c r="C18" s="26" t="s">
-        <v>5</v>
-      </c>
       <c r="D18" s="17"/>
-      <c r="E18" s="26" t="s">
+      <c r="F18" s="17"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="13"/>
+    </row>
+    <row r="19" spans="2:8" ht="99" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="11"/>
+      <c r="C19" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="F18" s="17"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="13"/>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="11"/>
-      <c r="C19" s="33"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="33"/>
-      <c r="G19" s="33"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="53"/>
+      <c r="G19" s="54"/>
       <c r="H19" s="13"/>
     </row>
-    <row r="20" spans="2:8" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="27"/>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="28"/>
+    <row r="20" spans="2:8" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="26"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="B10:B12"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="C20:G20"/>
     <mergeCell ref="C14:G14"/>
     <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C16:G16"/>
     <mergeCell ref="C19:G19"/>
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="C7:G7"/>
@@ -1112,7 +1246,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0.39370078740157483" top="0" bottom="0" header="0" footer="0"/>
-  <pageSetup paperSize="9" fitToWidth="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <headerFooter scaleWithDoc="0"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
